--- a/SGI_Sistema-de-gestao-integrado/SGE_Sistema-de-gestao-da-energia/Registos_SGE_Plasticom/SGE-05_IDE_LBE_Objetivos_Metas.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGE_Sistema-de-gestao-da-energia/Registos_SGE_Plasticom/SGE-05_IDE_LBE_Objetivos_Metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGE_Sistema-de-gestao-da-energia\Registos_SGE_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15815FF1-6737-431B-B810-B9E74F68936D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8427CCA4-7E48-4B5A-AC49-DDF36EB2B296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4335,7 +4335,7 @@
     <t>Fator estático</t>
   </si>
   <si>
-    <t>Entrada em produção de 4 máquinas novas (IM-007, IM-008, ISBM-009, ISBM-010) — ALT-2026-03 (linhas alimentar e farmacêutica).</t>
+    <t>Entrada em produção de 5 máquinas novas (IM-007, IM-008, IM-009, ISBM-009, ISBM-010) — ALT-2026-03 (linhas alimentar e farmacêutica).</t>
   </si>
   <si>
     <t>Ajuste não rotineiro (ISO 50006 §9.2): a energia atribuível às máquinas novas (horas × kW do RG-SGA-13 + quota de ar e frio) é retirada do real e as suas unidades das variáveis; fronteira do IDE-01 = instalação existente.</t>
@@ -6850,7 +6850,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F3ED-49BB-9350-CE3AD586EC52}"/>
+              <c16:uniqueId val="{00000000-A7EB-43EF-9416-E3692184ADBC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7029,7 +7029,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F3ED-49BB-9350-CE3AD586EC52}"/>
+              <c16:uniqueId val="{00000001-A7EB-43EF-9416-E3692184ADBC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7300,7 +7300,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A4F1-4A86-B5FB-5E949CC3C564}"/>
+              <c16:uniqueId val="{00000000-7566-4814-862D-FD93075665F1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
